--- a/data/attendance/ECOLE_بن_يحي_1AM.xlsx
+++ b/data/attendance/ECOLE_بن_يحي_1AM.xlsx
@@ -31,12 +31,40 @@
         </r>
       </text>
     </comment>
+    <comment ref="B7" authorId="0">
+      <text>
+        <r>
+          <t>student_id:046012c8-74c2-4262-a72a-710ed91f7078</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0">
+      <text>
+        <r>
+          <t>student_id:427a7b9a-4196-42dd-973f-1af9de7db99c</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0">
+      <text>
+        <r>
+          <t>student_id:4fd71b60-ae31-4326-ad60-fb0303115715</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0">
+      <text>
+        <r>
+          <t>student_id:044305fd-b3a9-4517-b44a-6e5b939e695a</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
   <si>
     <t>بن يحي 1AM  |  ECOLE  |  1AM  |  بن يحيى عبد النور</t>
   </si>
@@ -50,6 +78,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -59,6 +90,9 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
+    <t>29/09/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -68,6 +102,18 @@
     <t>فارس منيسا</t>
   </si>
   <si>
+    <t>tt tt</t>
+  </si>
+  <si>
+    <t>لبعيلي  محمد فراس</t>
+  </si>
+  <si>
+    <t>بن داود  سفيان</t>
+  </si>
+  <si>
+    <t>شيبوط لينا</t>
+  </si>
+  <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
   </si>
   <si>
@@ -95,7 +141,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -585,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -611,7 +660,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -621,10 +670,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -666,46 +718,46 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -713,7 +765,7 @@
         <v>818</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -757,7 +809,7 @@
         <v>819</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="9">
         <v>0</v>
@@ -793,6 +845,182 @@
         <v>0</v>
       </c>
       <c r="N6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>901</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8">
+        <v>0</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>972</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>976</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8">
+        <v>0</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0</v>
+      </c>
+      <c r="N9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>977</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9">
         <v>0</v>
       </c>
     </row>
@@ -812,7 +1040,7 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
@@ -820,77 +1048,82 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
